--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\NITW-Transportation-Division-main\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A306AD5-5B85-4D53-B054-5C3435189AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55A4FD-B23B-4777-ABF4-BA39899C68C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
   <si>
     <t>Name</t>
   </si>
@@ -72,15 +72,6 @@
     <t>brkadali@nitw.ac.in</t>
   </si>
   <si>
-    <t>Traffic, Safety, Behaviour, Sustainability</t>
-  </si>
-  <si>
-    <t>https://www.nitw.ac.in/CIVDeptAssets/images/37.jpg</t>
-  </si>
-  <si>
-    <t>M Hari Bharghav</t>
-  </si>
-  <si>
     <t>Technical Assistant</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>https://www.nitw.ac.in/CIVDeptAssets/images/st9.jpg</t>
   </si>
   <si>
-    <t>Kalumula Ramesh</t>
-  </si>
-  <si>
     <t>Senior Technical Assistant</t>
   </si>
   <si>
@@ -103,6 +91,186 @@
   </si>
   <si>
     <t>Image</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-csrk</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-brkadali</t>
+  </si>
+  <si>
+    <t>Prof. Vishnu R</t>
+  </si>
+  <si>
+    <t>vsr@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Pavement Materials, Pavement Management Systems, Pavement Design and Evaluation</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-vsr</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-vsr</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-brkadali</t>
+  </si>
+  <si>
+    <t>Prof. Arpan Mehar</t>
+  </si>
+  <si>
+    <t>Associate Professor</t>
+  </si>
+  <si>
+    <t>arpan@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Macroscopic and microscopic traffic analysis, Highway Capacity and level of service, Highway geometric design, Traffic flow simulation, Traffic pollution</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-arpan</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-arpan</t>
+  </si>
+  <si>
+    <t>Prof. K. V. R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>ravikvr@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Safety Analysis of Vehicular Interactions;Pedestrian behavioral analysis and modeling;Crowd dynamic analysis and emergency evacuation planning;Non-lane based behavior modeling and nanoscopic model development; Capacity analysis of highways under mixed traffic conditions;</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-ravikvr</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-ravikvr</t>
+  </si>
+  <si>
+    <t>Sri. Kalumula Ramesh</t>
+  </si>
+  <si>
+    <t>Sri. M Hari Bharghav</t>
+  </si>
+  <si>
+    <t>Sri. Md. Abdul Gaffar</t>
+  </si>
+  <si>
+    <t>Senior Technician</t>
+  </si>
+  <si>
+    <t>mdgaffar833296@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.nitw.ac.in/CIVDeptAssets/images/st12.jpg</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Dr. Martin Ekse</t>
+  </si>
+  <si>
+    <t>Dr. V.V. Silyanov MADI, Moscow, Russia</t>
+  </si>
+  <si>
+    <t>Dr. K.S. Pillai</t>
+  </si>
+  <si>
+    <t>Dr. S. Raghava Chari</t>
+  </si>
+  <si>
+    <t>Dr. B.K. Marwah</t>
+  </si>
+  <si>
+    <t>Dr. T.S. Reddy</t>
+  </si>
+  <si>
+    <t>Sri D. Sanyal</t>
+  </si>
+  <si>
+    <t>Sri A.K. Bandopadhyay</t>
+  </si>
+  <si>
+    <t>Sri N.K. Lohani</t>
+  </si>
+  <si>
+    <t>Sri P.V. Ramana Moorthy</t>
+  </si>
+  <si>
+    <t>Dr. B.P. Chandrasekhar</t>
+  </si>
+  <si>
+    <t>Dr. T.V. Ramanayya</t>
+  </si>
+  <si>
+    <t>Sri S. Venkatesh</t>
+  </si>
+  <si>
+    <t>Sri P. Satyanarayana</t>
+  </si>
+  <si>
+    <t>Dr. N.V. Rama Moorthy</t>
+  </si>
+  <si>
+    <t>Dr. K.M. Badarinath</t>
+  </si>
+  <si>
+    <t>Dr. Francis Christopher</t>
+  </si>
+  <si>
+    <t>Sri K. Appala Raju (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Sri D.B. Srinivas (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Sri V.R. Vinayaka Rao (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Sri N. Sadguna (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Sri B.V. Kiran Kumar (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Dr. S.S.S.V. Gopala Raju (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Ms B. Sireesha (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Sri N. Vishnu Prasad (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Ms. M. Rama Lakshmi (Ad hoc)</t>
+  </si>
+  <si>
+    <t>Dr. D.S.N.V. Amar Kumar</t>
+  </si>
+  <si>
+    <t>Dr. K.V.R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Prof. T.V. Ramanayya (Visiting Professor)</t>
+  </si>
+  <si>
+    <t>Dr. P. Sasanka Bhushan (Ad hoc)</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Pedestrian Cross Flow Modelling, Non-Motorized Safety, Traffic Safety, Driver Behaviour, Traffic flow modeling • Transportation Environment • Travel behavior, Sustainable Transportation • Freight Transportation</t>
   </si>
 </sst>
 </file>
@@ -438,19 +606,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,30 +635,36 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>8332969421</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -504,24 +678,99 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>8332969262</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G6">
+    <sortCondition ref="A2:A6"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{E5822289-CFEA-422D-AC65-BCF8A3E05343}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{E5822289-CFEA-422D-AC65-BCF8A3E05343}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{F776B85C-FD73-46BF-85F1-C6C749158FA3}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{51DD2074-866B-453C-9084-5D9B38722E68}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{EDD927B0-11EA-4F61-B44F-01306BE1BCF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171B638D-414D-4996-840E-64470368FA75}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -545,46 +794,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2">
-        <v>8328383763</v>
+        <v>8332969268</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>8332969268</v>
+        <v>8328383763</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>8332969280</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
+    <sortCondition ref="A2:A4"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{8D44F718-BAC3-49F5-A088-70BB1D22A014}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{8D44F718-BAC3-49F5-A088-70BB1D22A014}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -592,18 +861,458 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D969DC-6FC0-4E4D-B105-6F6F4232277C}">
-  <dimension ref="A1"/>
+  <dimension ref="D3:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="3" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905C8B99-C97A-471D-B4C9-6820D7F138E5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2">
+        <v>1969</v>
+      </c>
+      <c r="D2">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3">
+        <v>1972</v>
+      </c>
+      <c r="D3">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4">
+        <v>1969</v>
+      </c>
+      <c r="D4">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5">
+        <v>1969</v>
+      </c>
+      <c r="D5">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6">
+        <v>1972</v>
+      </c>
+      <c r="D6">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>1963</v>
+      </c>
+      <c r="D7">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8">
+        <v>1969</v>
+      </c>
+      <c r="D8">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9">
+        <v>1969</v>
+      </c>
+      <c r="D9">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10">
+        <v>1970</v>
+      </c>
+      <c r="D10">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11">
+        <v>1970</v>
+      </c>
+      <c r="D11">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12">
+        <v>1970</v>
+      </c>
+      <c r="D12">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13">
+        <v>1971</v>
+      </c>
+      <c r="D13">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14">
+        <v>1971</v>
+      </c>
+      <c r="D14">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15">
+        <v>1973</v>
+      </c>
+      <c r="D15">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16">
+        <v>1973</v>
+      </c>
+      <c r="D16">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>1974</v>
+      </c>
+      <c r="D17">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>1979</v>
+      </c>
+      <c r="D18">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19">
+        <v>1982</v>
+      </c>
+      <c r="D19">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20">
+        <v>1982</v>
+      </c>
+      <c r="D20">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>1992</v>
+      </c>
+      <c r="D21">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22">
+        <v>1992</v>
+      </c>
+      <c r="D22">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23">
+        <v>2002</v>
+      </c>
+      <c r="D23">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24">
+        <v>2000</v>
+      </c>
+      <c r="D24">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25">
+        <v>2000</v>
+      </c>
+      <c r="D25">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26">
+        <v>2002</v>
+      </c>
+      <c r="D26">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27">
+        <v>2003</v>
+      </c>
+      <c r="D27">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28">
+        <v>2004</v>
+      </c>
+      <c r="D28">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29">
+        <v>2004</v>
+      </c>
+      <c r="D29">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30">
+        <v>2013</v>
+      </c>
+      <c r="D30">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31">
+        <v>2013</v>
+      </c>
+      <c r="D31">
+        <v>2017</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55A4FD-B23B-4777-ABF4-BA39899C68C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB9B819-57FE-468B-A5CC-FE9B6D8B7DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -271,6 +271,39 @@
   </si>
   <si>
     <t>Pedestrian Cross Flow Modelling, Non-Motorized Safety, Traffic Safety, Driver Behaviour, Traffic flow modeling • Transportation Environment • Travel behavior, Sustainable Transportation • Freight Transportation</t>
+  </si>
+  <si>
+    <t>Prof. Venkaiah Chowdary</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>vc@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Characterization for asphalt binders and mixtures; asphalt pavement analysis, design and evaluation; quantification of roadway and railway traffic noise.</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-vc</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-vc</t>
+  </si>
+  <si>
+    <t>Prof. S. Shankar</t>
+  </si>
+  <si>
+    <t>ss@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Low Volume Roads, Pavement Analysis and Design, Pavement Management System, Pavement Material characterization, Geo-Synthetic Applications in Pavements and Marginal and Innovative Materials in LVRs</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-ss</t>
+  </si>
+  <si>
+    <t>https://erp.nitw.ac.in/ext/profile/ce-ss</t>
   </si>
 </sst>
 </file>
@@ -606,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -735,36 +768,86 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>9849102935</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>8332969252</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G8" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G6">
-    <sortCondition ref="A2:A6"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
+    <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{E5822289-CFEA-422D-AC65-BCF8A3E05343}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{F776B85C-FD73-46BF-85F1-C6C749158FA3}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{51DD2074-866B-453C-9084-5D9B38722E68}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{EDD927B0-11EA-4F61-B44F-01306BE1BCF1}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{AF349A3B-65A6-4BED-A302-FEA82F060327}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{EE795596-A6E6-4391-AB06-1414421C11AD}"/>
+    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{3D758237-1E6D-4D2D-8FDA-8431CAFEB283}"/>
+    <hyperlink ref="F6" r:id="rId8" xr:uid="{3EDEE717-2E36-473B-8A47-61F2C9ED6B20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB9B819-57FE-468B-A5CC-FE9B6D8B7DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BB82E1-A9B5-4A7F-B0B4-E1C6030D35B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -304,13 +304,169 @@
   </si>
   <si>
     <t>https://erp.nitw.ac.in/ext/profile/ce-ss</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Research Areas</t>
+  </si>
+  <si>
+    <t>faculty1.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Ananya Sharma</t>
+  </si>
+  <si>
+    <t>+91 98765 43210</t>
+  </si>
+  <si>
+    <t>ananya.sharma@university.edu</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Machine Learning, Data Analytics</t>
+  </si>
+  <si>
+    <t>faculty2.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Rahul Verma</t>
+  </si>
+  <si>
+    <t>+91 98765 43211</t>
+  </si>
+  <si>
+    <t>rahul.verma@university.edu</t>
+  </si>
+  <si>
+    <t>Computer Vision, Image Processing, Deep Learning</t>
+  </si>
+  <si>
+    <t>faculty3.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Priya Nair</t>
+  </si>
+  <si>
+    <t>+91 98765 43212</t>
+  </si>
+  <si>
+    <t>priya.nair@university.edu</t>
+  </si>
+  <si>
+    <t>Cyber Security, Network Security, Cryptography</t>
+  </si>
+  <si>
+    <t>faculty4.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Karthik Reddy</t>
+  </si>
+  <si>
+    <t>+91 98765 43213</t>
+  </si>
+  <si>
+    <t>karthik.reddy@university.edu</t>
+  </si>
+  <si>
+    <t>Internet of Things (IoT), Embedded Systems</t>
+  </si>
+  <si>
+    <t>faculty5.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Sneha Gupta</t>
+  </si>
+  <si>
+    <t>+91 98765 43214</t>
+  </si>
+  <si>
+    <t>sneha.gupta@university.edu</t>
+  </si>
+  <si>
+    <t>Natural Language Processing, Generative AI</t>
+  </si>
+  <si>
+    <t>faculty6.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Arjun Mehta</t>
+  </si>
+  <si>
+    <t>+91 98765 43215</t>
+  </si>
+  <si>
+    <t>arjun.mehta@university.edu</t>
+  </si>
+  <si>
+    <t>Big Data Analytics, Cloud Computing</t>
+  </si>
+  <si>
+    <t>faculty7.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Neha Kapoor</t>
+  </si>
+  <si>
+    <t>+91 98765 43216</t>
+  </si>
+  <si>
+    <t>neha.kapoor@university.edu</t>
+  </si>
+  <si>
+    <t>Human-Computer Interaction, UX Design</t>
+  </si>
+  <si>
+    <t>faculty8.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Vikram Singh</t>
+  </si>
+  <si>
+    <t>+91 98765 43217</t>
+  </si>
+  <si>
+    <t>vikram.singh@university.edu</t>
+  </si>
+  <si>
+    <t>Robotics, Autonomous Systems</t>
+  </si>
+  <si>
+    <t>faculty9.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Pooja Menon</t>
+  </si>
+  <si>
+    <t>+91 98765 43218</t>
+  </si>
+  <si>
+    <t>pooja.menon@university.edu</t>
+  </si>
+  <si>
+    <t>Data Science, Business Intelligence</t>
+  </si>
+  <si>
+    <t>faculty10.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Rohan Das</t>
+  </si>
+  <si>
+    <t>+91 98765 43219</t>
+  </si>
+  <si>
+    <t>rohan.das@university.edu</t>
+  </si>
+  <si>
+    <t>Software Engineering, Distributed Systems</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +487,14 @@
       <color rgb="FF212529"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -354,10 +518,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -944,12 +1114,236 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D969DC-6FC0-4E4D-B105-6F6F4232277C}">
-  <dimension ref="D3:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D3" s="2"/>
-      <c r="F3" s="2"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BB82E1-A9B5-4A7F-B0B4-E1C6030D35B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EE9337-1F16-47D7-AF33-F9D193924AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -872,7 +872,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>8879425755</v>
@@ -918,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>8332969262</v>
@@ -941,7 +941,7 @@
         <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>9849102935</v>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EE9337-1F16-47D7-AF33-F9D193924AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA08F108-13DC-486E-8FF0-05E21A9A6674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
     <sheet name="Staff" sheetId="2" r:id="rId2"/>
     <sheet name="GuestFaculty" sheetId="3" r:id="rId3"/>
-    <sheet name="Previous" sheetId="4" r:id="rId4"/>
+    <sheet name="PreviousFaculty" sheetId="4" r:id="rId4"/>
+    <sheet name="PreviousHOD" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
   <si>
     <t>Name</t>
   </si>
@@ -460,13 +461,46 @@
   </si>
   <si>
     <t>Software Engineering, Distributed Systems</t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>Prof. M. Venkata Ratnam</t>
+  </si>
+  <si>
+    <t>Prof. K.S. Pillai</t>
+  </si>
+  <si>
+    <t>Prof. S. Raghava Chari</t>
+  </si>
+  <si>
+    <t>Prof. B.P. Chandrasekhar</t>
+  </si>
+  <si>
+    <t>Prof. NV Rama Moorthy</t>
+  </si>
+  <si>
+    <t>Dr. C.S.R.K. Prasad</t>
+  </si>
+  <si>
+    <t>Dr. Venkaiah Chowdary</t>
+  </si>
+  <si>
+    <t>Dr. K.V. R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Dr. S. Shankar</t>
+  </si>
+  <si>
+    <t>Till date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +530,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -505,7 +552,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -513,12 +560,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -527,6 +626,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1352,10 +1466,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905C8B99-C97A-471D-B4C9-6820D7F138E5}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>79</v>
       </c>
@@ -1368,8 +1486,11 @@
       <c r="D1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1382,8 +1503,11 @@
       <c r="D2">
         <v>1970</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1396,8 +1520,11 @@
       <c r="D3">
         <v>1973</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1410,8 +1537,11 @@
       <c r="D4">
         <v>1978</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1424,8 +1554,11 @@
       <c r="D5">
         <v>1970</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1438,8 +1571,11 @@
       <c r="D6">
         <v>1973</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1452,8 +1588,11 @@
       <c r="D7">
         <v>1978</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1466,8 +1605,11 @@
       <c r="D8">
         <v>1997</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1480,8 +1622,11 @@
       <c r="D9">
         <v>1970</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1494,8 +1639,11 @@
       <c r="D10">
         <v>1971</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1508,8 +1656,11 @@
       <c r="D11">
         <v>1972</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1522,8 +1673,11 @@
       <c r="D12">
         <v>1973</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1536,8 +1690,11 @@
       <c r="D13">
         <v>1972</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1550,8 +1707,11 @@
       <c r="D14">
         <v>1980</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1564,8 +1724,11 @@
       <c r="D15">
         <v>2007</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1578,8 +1741,11 @@
       <c r="D16">
         <v>1981</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1592,8 +1758,11 @@
       <c r="D17">
         <v>1975</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1606,8 +1775,11 @@
       <c r="D18">
         <v>1981</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1620,8 +1792,11 @@
       <c r="D19">
         <v>2007</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1634,8 +1809,11 @@
       <c r="D20">
         <v>1991</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1648,8 +1826,11 @@
       <c r="D21">
         <v>1993</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1662,8 +1843,11 @@
       <c r="D22">
         <v>1993</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1676,8 +1860,11 @@
       <c r="D23">
         <v>2003</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1690,8 +1877,11 @@
       <c r="D24">
         <v>2003</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1704,8 +1894,11 @@
       <c r="D25">
         <v>2004</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1718,8 +1911,11 @@
       <c r="D26">
         <v>2003</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1732,8 +1928,11 @@
       <c r="D27">
         <v>2004</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1746,8 +1945,11 @@
       <c r="D28">
         <v>2005</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1760,8 +1962,11 @@
       <c r="D29">
         <v>2005</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1774,8 +1979,11 @@
       <c r="D30">
         <v>2013</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1787,9 +1995,333 @@
       </c>
       <c r="D31">
         <v>2017</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D5A469-D3C9-4402-8F35-E4A79309EE57}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1968</v>
+      </c>
+      <c r="D2" s="9">
+        <v>1970</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1970</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1978</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1978</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1987</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1987</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1990</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1990</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1993</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1993</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1996</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1996</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1999</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1999</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="9">
+        <v>2002</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2005</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2006</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2018</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2022</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2024</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA08F108-13DC-486E-8FF0-05E21A9A6674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7855879-5D8C-42F9-A939-52E9C584BF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="145">
   <si>
     <t>Name</t>
   </si>
@@ -313,9 +313,6 @@
     <t>Research Areas</t>
   </si>
   <si>
-    <t>faculty1.jpg</t>
-  </si>
-  <si>
     <t>Dr. Ananya Sharma</t>
   </si>
   <si>
@@ -328,9 +325,6 @@
     <t>Artificial Intelligence, Machine Learning, Data Analytics</t>
   </si>
   <si>
-    <t>faculty2.jpg</t>
-  </si>
-  <si>
     <t>Dr. Rahul Verma</t>
   </si>
   <si>
@@ -343,9 +337,6 @@
     <t>Computer Vision, Image Processing, Deep Learning</t>
   </si>
   <si>
-    <t>faculty3.jpg</t>
-  </si>
-  <si>
     <t>Dr. Priya Nair</t>
   </si>
   <si>
@@ -358,9 +349,6 @@
     <t>Cyber Security, Network Security, Cryptography</t>
   </si>
   <si>
-    <t>faculty4.jpg</t>
-  </si>
-  <si>
     <t>Dr. Karthik Reddy</t>
   </si>
   <si>
@@ -373,9 +361,6 @@
     <t>Internet of Things (IoT), Embedded Systems</t>
   </si>
   <si>
-    <t>faculty5.jpg</t>
-  </si>
-  <si>
     <t>Dr. Sneha Gupta</t>
   </si>
   <si>
@@ -388,9 +373,6 @@
     <t>Natural Language Processing, Generative AI</t>
   </si>
   <si>
-    <t>faculty6.jpg</t>
-  </si>
-  <si>
     <t>Dr. Arjun Mehta</t>
   </si>
   <si>
@@ -403,9 +385,6 @@
     <t>Big Data Analytics, Cloud Computing</t>
   </si>
   <si>
-    <t>faculty7.jpg</t>
-  </si>
-  <si>
     <t>Dr. Neha Kapoor</t>
   </si>
   <si>
@@ -418,9 +397,6 @@
     <t>Human-Computer Interaction, UX Design</t>
   </si>
   <si>
-    <t>faculty8.jpg</t>
-  </si>
-  <si>
     <t>Dr. Vikram Singh</t>
   </si>
   <si>
@@ -433,9 +409,6 @@
     <t>Robotics, Autonomous Systems</t>
   </si>
   <si>
-    <t>faculty9.jpg</t>
-  </si>
-  <si>
     <t>Dr. Pooja Menon</t>
   </si>
   <si>
@@ -446,9 +419,6 @@
   </si>
   <si>
     <t>Data Science, Business Intelligence</t>
-  </si>
-  <si>
-    <t>faculty10.jpg</t>
   </si>
   <si>
     <t>Dr. Rohan Das</t>
@@ -1261,203 +1231,183 @@
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>104</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="4" t="s">
         <v>109</v>
       </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>114</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>124</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1503,9 +1453,7 @@
       <c r="D2">
         <v>1970</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1520,9 +1468,7 @@
       <c r="D3">
         <v>1973</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -1537,9 +1483,7 @@
       <c r="D4">
         <v>1978</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1554,9 +1498,7 @@
       <c r="D5">
         <v>1970</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1571,9 +1513,7 @@
       <c r="D6">
         <v>1973</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>114</v>
-      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1588,9 +1528,7 @@
       <c r="D7">
         <v>1978</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>119</v>
-      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1605,9 +1543,7 @@
       <c r="D8">
         <v>1997</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>124</v>
-      </c>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1622,9 +1558,7 @@
       <c r="D9">
         <v>1970</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1639,9 +1573,7 @@
       <c r="D10">
         <v>1971</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -1656,9 +1588,7 @@
       <c r="D11">
         <v>1972</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -1673,9 +1603,7 @@
       <c r="D12">
         <v>1973</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -1690,9 +1618,7 @@
       <c r="D13">
         <v>1972</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -1707,9 +1633,7 @@
       <c r="D14">
         <v>1980</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -1724,9 +1648,7 @@
       <c r="D15">
         <v>2007</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -1741,9 +1663,7 @@
       <c r="D16">
         <v>1981</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
@@ -1758,9 +1678,7 @@
       <c r="D17">
         <v>1975</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -1775,9 +1693,7 @@
       <c r="D18">
         <v>1981</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -1792,9 +1708,7 @@
       <c r="D19">
         <v>2007</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -1809,9 +1723,7 @@
       <c r="D20">
         <v>1991</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -1826,9 +1738,7 @@
       <c r="D21">
         <v>1993</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -1843,9 +1753,7 @@
       <c r="D22">
         <v>1993</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1860,9 +1768,7 @@
       <c r="D23">
         <v>2003</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -1877,9 +1783,7 @@
       <c r="D24">
         <v>2003</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1894,9 +1798,7 @@
       <c r="D25">
         <v>2004</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1911,9 +1813,7 @@
       <c r="D26">
         <v>2003</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -1928,9 +1828,7 @@
       <c r="D27">
         <v>2004</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1945,9 +1843,7 @@
       <c r="D28">
         <v>2005</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -1962,9 +1858,7 @@
       <c r="D29">
         <v>2005</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1979,9 +1873,7 @@
       <c r="D30">
         <v>2013</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -1996,9 +1888,7 @@
       <c r="D31">
         <v>2017</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2019,7 +1909,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2039,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C2" s="9">
         <v>1968</v>
@@ -2047,16 +1937,14 @@
       <c r="D2" s="9">
         <v>1970</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C3" s="9">
         <v>1970</v>
@@ -2064,16 +1952,14 @@
       <c r="D3" s="9">
         <v>1978</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9">
         <v>1978</v>
@@ -2081,16 +1967,14 @@
       <c r="D4" s="9">
         <v>1987</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9">
         <v>1987</v>
@@ -2098,16 +1982,14 @@
       <c r="D5" s="9">
         <v>1990</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C6" s="9">
         <v>1990</v>
@@ -2115,16 +1997,14 @@
       <c r="D6" s="9">
         <v>1993</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>114</v>
-      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C7" s="9">
         <v>1993</v>
@@ -2132,16 +2012,14 @@
       <c r="D7" s="9">
         <v>1996</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>119</v>
-      </c>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C8" s="9">
         <v>1996</v>
@@ -2149,16 +2027,14 @@
       <c r="D8" s="9">
         <v>1999</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>124</v>
-      </c>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C9" s="9">
         <v>1999</v>
@@ -2166,16 +2042,14 @@
       <c r="D9" s="9">
         <v>2002</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C10" s="9">
         <v>2002</v>
@@ -2183,16 +2057,14 @@
       <c r="D10" s="9">
         <v>2005</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C11" s="9">
         <v>2005</v>
@@ -2200,16 +2072,14 @@
       <c r="D11" s="9">
         <v>2006</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C12" s="9">
         <v>2006</v>
@@ -2217,16 +2087,14 @@
       <c r="D12" s="9">
         <v>2018</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C13" s="9">
         <v>2018</v>
@@ -2234,16 +2102,14 @@
       <c r="D13" s="9">
         <v>2022</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C14" s="9">
         <v>2022</v>
@@ -2251,26 +2117,22 @@
       <c r="D14" s="9">
         <v>2024</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E16" s="4"/>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7855879-5D8C-42F9-A939-52E9C584BF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="10350" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
     <sheet name="Staff" sheetId="2" r:id="rId2"/>
     <sheet name="GuestFaculty" sheetId="3" r:id="rId3"/>
-    <sheet name="PreviousFaculty" sheetId="4" r:id="rId4"/>
-    <sheet name="PreviousHOD" sheetId="5" r:id="rId5"/>
+    <sheet name="Previous" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
   <si>
     <t>Name</t>
   </si>
@@ -178,9 +176,6 @@
     <t>To</t>
   </si>
   <si>
-    <t>Dr. Martin Ekse</t>
-  </si>
-  <si>
     <t>Dr. V.V. Silyanov MADI, Moscow, Russia</t>
   </si>
   <si>
@@ -259,9 +254,6 @@
     <t>Dr. D.S.N.V. Amar Kumar</t>
   </si>
   <si>
-    <t>Dr. K.V.R. Ravi Shankar</t>
-  </si>
-  <si>
     <t>Prof. T.V. Ramanayya (Visiting Professor)</t>
   </si>
   <si>
@@ -313,6 +305,9 @@
     <t>Research Areas</t>
   </si>
   <si>
+    <t>faculty1.jpg</t>
+  </si>
+  <si>
     <t>Dr. Ananya Sharma</t>
   </si>
   <si>
@@ -325,6 +320,9 @@
     <t>Artificial Intelligence, Machine Learning, Data Analytics</t>
   </si>
   <si>
+    <t>faculty2.jpg</t>
+  </si>
+  <si>
     <t>Dr. Rahul Verma</t>
   </si>
   <si>
@@ -337,6 +335,9 @@
     <t>Computer Vision, Image Processing, Deep Learning</t>
   </si>
   <si>
+    <t>faculty3.jpg</t>
+  </si>
+  <si>
     <t>Dr. Priya Nair</t>
   </si>
   <si>
@@ -349,6 +350,9 @@
     <t>Cyber Security, Network Security, Cryptography</t>
   </si>
   <si>
+    <t>faculty4.jpg</t>
+  </si>
+  <si>
     <t>Dr. Karthik Reddy</t>
   </si>
   <si>
@@ -361,6 +365,9 @@
     <t>Internet of Things (IoT), Embedded Systems</t>
   </si>
   <si>
+    <t>faculty5.jpg</t>
+  </si>
+  <si>
     <t>Dr. Sneha Gupta</t>
   </si>
   <si>
@@ -373,6 +380,9 @@
     <t>Natural Language Processing, Generative AI</t>
   </si>
   <si>
+    <t>faculty6.jpg</t>
+  </si>
+  <si>
     <t>Dr. Arjun Mehta</t>
   </si>
   <si>
@@ -385,6 +395,9 @@
     <t>Big Data Analytics, Cloud Computing</t>
   </si>
   <si>
+    <t>faculty7.jpg</t>
+  </si>
+  <si>
     <t>Dr. Neha Kapoor</t>
   </si>
   <si>
@@ -397,6 +410,9 @@
     <t>Human-Computer Interaction, UX Design</t>
   </si>
   <si>
+    <t>faculty8.jpg</t>
+  </si>
+  <si>
     <t>Dr. Vikram Singh</t>
   </si>
   <si>
@@ -409,6 +425,9 @@
     <t>Robotics, Autonomous Systems</t>
   </si>
   <si>
+    <t>faculty9.jpg</t>
+  </si>
+  <si>
     <t>Dr. Pooja Menon</t>
   </si>
   <si>
@@ -421,6 +440,9 @@
     <t>Data Science, Business Intelligence</t>
   </si>
   <si>
+    <t>faculty10.jpg</t>
+  </si>
+  <si>
     <t>Dr. Rohan Das</t>
   </si>
   <si>
@@ -433,44 +455,14 @@
     <t>Software Engineering, Distributed Systems</t>
   </si>
   <si>
-    <t>S. No.</t>
-  </si>
-  <si>
-    <t>Prof. M. Venkata Ratnam</t>
-  </si>
-  <si>
-    <t>Prof. K.S. Pillai</t>
-  </si>
-  <si>
-    <t>Prof. S. Raghava Chari</t>
-  </si>
-  <si>
-    <t>Prof. B.P. Chandrasekhar</t>
-  </si>
-  <si>
-    <t>Prof. NV Rama Moorthy</t>
-  </si>
-  <si>
-    <t>Dr. C.S.R.K. Prasad</t>
-  </si>
-  <si>
-    <t>Dr. Venkaiah Chowdary</t>
-  </si>
-  <si>
-    <t>Dr. K.V. R. Ravi Shankar</t>
-  </si>
-  <si>
-    <t>Dr. S. Shankar</t>
-  </si>
-  <si>
-    <t>Till date</t>
+    <t>Dr. Martin Ekse, Washington University, USA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,19 +492,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -522,7 +501,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -530,64 +509,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -596,21 +523,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -892,13 +804,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49.28515625" bestFit="1" customWidth="1"/>
@@ -956,7 +868,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>8879425755</v>
@@ -965,7 +877,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>29</v>
@@ -1002,7 +914,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>8332969262</v>
@@ -1022,48 +934,48 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>9849102935</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>89</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>8332969252</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>84</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1087,18 +999,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
+  <sortState ref="A2:G8">
     <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{E5822289-CFEA-422D-AC65-BCF8A3E05343}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{F776B85C-FD73-46BF-85F1-C6C749158FA3}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{51DD2074-866B-453C-9084-5D9B38722E68}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{EDD927B0-11EA-4F61-B44F-01306BE1BCF1}"/>
-    <hyperlink ref="D7" r:id="rId5" xr:uid="{AF349A3B-65A6-4BED-A302-FEA82F060327}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{EE795596-A6E6-4391-AB06-1414421C11AD}"/>
-    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{3D758237-1E6D-4D2D-8FDA-8431CAFEB283}"/>
-    <hyperlink ref="F6" r:id="rId8" xr:uid="{3EDEE717-2E36-473B-8A47-61F2C9ED6B20}"/>
+    <hyperlink ref="D4" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="F3" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D7" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in"/>
+    <hyperlink ref="F6" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1106,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171B638D-414D-4996-840E-64470368FA75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1186,18 +1098,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
+  <sortState ref="A2:E4">
     <sortCondition ref="A2:A4"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{8D44F718-BAC3-49F5-A088-70BB1D22A014}"/>
+    <hyperlink ref="E3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D969DC-6FC0-4E4D-B105-6F6F4232277C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1220,10 +1132,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>20</v>
@@ -1231,21 +1143,23 @@
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1263,151 +1177,169 @@
       <c r="E3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="4"/>
+        <v>126</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="4"/>
+        <v>141</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1415,17 +1347,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905C8B99-C97A-471D-B4C9-6820D7F138E5}">
-  <dimension ref="A1:E31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1436,16 +1367,13 @@
       <c r="D1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1453,14 +1381,13 @@
       <c r="D2">
         <v>1970</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>1972</v>
@@ -1468,299 +1395,279 @@
       <c r="D3">
         <v>1973</v>
       </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="D4">
         <v>1978</v>
       </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>1969</v>
       </c>
       <c r="D5">
-        <v>1970</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="D6">
-        <v>1973</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>1963</v>
+        <v>1970</v>
       </c>
       <c r="D7">
-        <v>1978</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D8">
-        <v>1997</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D9">
-        <v>1970</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D10">
-        <v>1971</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D11">
-        <v>1972</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D12">
-        <v>1973</v>
-      </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="D13">
-        <v>1972</v>
-      </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="D14">
-        <v>1980</v>
-      </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="D15">
-        <v>2007</v>
-      </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="D16">
-        <v>1981</v>
-      </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="D17">
-        <v>1975</v>
-      </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D18">
-        <v>1981</v>
-      </c>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="D19">
-        <v>2007</v>
-      </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="D20">
-        <v>1991</v>
-      </c>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="D21">
-        <v>1993</v>
-      </c>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="D22">
-        <v>1993</v>
-      </c>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23">
         <v>2002</v>
@@ -1768,422 +1675,106 @@
       <c r="D23">
         <v>2003</v>
       </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D24">
-        <v>2003</v>
-      </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D25">
         <v>2004</v>
       </c>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D26">
-        <v>2003</v>
-      </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D27">
-        <v>2004</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="D28">
-        <v>2005</v>
-      </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="D29">
-        <v>2005</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30">
         <v>2013</v>
       </c>
       <c r="D30">
-        <v>2013</v>
-      </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31">
-        <v>2013</v>
-      </c>
-      <c r="D31">
         <v>2017</v>
       </c>
-      <c r="E31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D5A469-D3C9-4402-8F35-E4A79309EE57}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="9">
-        <v>1968</v>
-      </c>
-      <c r="D2" s="9">
-        <v>1970</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1970</v>
-      </c>
-      <c r="D3" s="9">
-        <v>1978</v>
-      </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1978</v>
-      </c>
-      <c r="D4" s="9">
-        <v>1987</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1987</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1990</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1990</v>
-      </c>
-      <c r="D6" s="9">
-        <v>1993</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1993</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1996</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1996</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1999</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1999</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2002</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="9">
-        <v>2002</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2005</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="9">
-        <v>2005</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2006</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="9">
-        <v>2006</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2018</v>
-      </c>
-      <c r="D13" s="9">
-        <v>2022</v>
-      </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2022</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2024</v>
-      </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="9">
-        <v>2024</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA9D0D2-C188-48FF-A065-F4F99C48089E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="10350" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
     <sheet name="Staff" sheetId="2" r:id="rId2"/>
     <sheet name="GuestFaculty" sheetId="3" r:id="rId3"/>
-    <sheet name="Previous" sheetId="4" r:id="rId4"/>
+    <sheet name="PreviousFaculty" sheetId="4" r:id="rId4"/>
+    <sheet name="PreviousHOD" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
   <si>
     <t>Name</t>
   </si>
@@ -176,6 +178,9 @@
     <t>To</t>
   </si>
   <si>
+    <t>Dr. Martin Ekse</t>
+  </si>
+  <si>
     <t>Dr. V.V. Silyanov MADI, Moscow, Russia</t>
   </si>
   <si>
@@ -254,6 +259,9 @@
     <t>Dr. D.S.N.V. Amar Kumar</t>
   </si>
   <si>
+    <t>Dr. K.V.R. Ravi Shankar</t>
+  </si>
+  <si>
     <t>Prof. T.V. Ramanayya (Visiting Professor)</t>
   </si>
   <si>
@@ -305,9 +313,6 @@
     <t>Research Areas</t>
   </si>
   <si>
-    <t>faculty1.jpg</t>
-  </si>
-  <si>
     <t>Dr. Ananya Sharma</t>
   </si>
   <si>
@@ -320,9 +325,6 @@
     <t>Artificial Intelligence, Machine Learning, Data Analytics</t>
   </si>
   <si>
-    <t>faculty2.jpg</t>
-  </si>
-  <si>
     <t>Dr. Rahul Verma</t>
   </si>
   <si>
@@ -335,9 +337,6 @@
     <t>Computer Vision, Image Processing, Deep Learning</t>
   </si>
   <si>
-    <t>faculty3.jpg</t>
-  </si>
-  <si>
     <t>Dr. Priya Nair</t>
   </si>
   <si>
@@ -350,9 +349,6 @@
     <t>Cyber Security, Network Security, Cryptography</t>
   </si>
   <si>
-    <t>faculty4.jpg</t>
-  </si>
-  <si>
     <t>Dr. Karthik Reddy</t>
   </si>
   <si>
@@ -365,9 +361,6 @@
     <t>Internet of Things (IoT), Embedded Systems</t>
   </si>
   <si>
-    <t>faculty5.jpg</t>
-  </si>
-  <si>
     <t>Dr. Sneha Gupta</t>
   </si>
   <si>
@@ -380,9 +373,6 @@
     <t>Natural Language Processing, Generative AI</t>
   </si>
   <si>
-    <t>faculty6.jpg</t>
-  </si>
-  <si>
     <t>Dr. Arjun Mehta</t>
   </si>
   <si>
@@ -395,9 +385,6 @@
     <t>Big Data Analytics, Cloud Computing</t>
   </si>
   <si>
-    <t>faculty7.jpg</t>
-  </si>
-  <si>
     <t>Dr. Neha Kapoor</t>
   </si>
   <si>
@@ -410,9 +397,6 @@
     <t>Human-Computer Interaction, UX Design</t>
   </si>
   <si>
-    <t>faculty8.jpg</t>
-  </si>
-  <si>
     <t>Dr. Vikram Singh</t>
   </si>
   <si>
@@ -425,9 +409,6 @@
     <t>Robotics, Autonomous Systems</t>
   </si>
   <si>
-    <t>faculty9.jpg</t>
-  </si>
-  <si>
     <t>Dr. Pooja Menon</t>
   </si>
   <si>
@@ -440,9 +421,6 @@
     <t>Data Science, Business Intelligence</t>
   </si>
   <si>
-    <t>faculty10.jpg</t>
-  </si>
-  <si>
     <t>Dr. Rohan Das</t>
   </si>
   <si>
@@ -455,14 +433,62 @@
     <t>Software Engineering, Distributed Systems</t>
   </si>
   <si>
-    <t>Dr. Martin Ekse, Washington University, USA</t>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>Prof. M. Venkata Ratnam</t>
+  </si>
+  <si>
+    <t>Prof. K.S. Pillai</t>
+  </si>
+  <si>
+    <t>Prof. S. Raghava Chari</t>
+  </si>
+  <si>
+    <t>Prof. B.P. Chandrasekhar</t>
+  </si>
+  <si>
+    <t>Prof. NV Rama Moorthy</t>
+  </si>
+  <si>
+    <t>Dr. C.S.R.K. Prasad</t>
+  </si>
+  <si>
+    <t>Dr. Venkaiah Chowdary</t>
+  </si>
+  <si>
+    <t>Dr. K.V. R. Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Dr. S. Shankar</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Till Date</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/D.B. Srinivas.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/V.R. Vinayaka Rao.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/B.V. Kiran Kumar.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/SSSV Gopal Raju.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/N. Sadguna.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +518,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -501,10 +540,82 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -514,7 +625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -524,6 +635,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -804,16 +937,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="102.7109375" customWidth="1"/>
     <col min="7" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -868,7 +1001,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>8879425755</v>
@@ -877,7 +1010,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>29</v>
@@ -914,7 +1047,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>8332969262</v>
@@ -934,48 +1067,48 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>9849102935</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>8332969252</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -999,18 +1132,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
     <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="F3" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D7" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in"/>
-    <hyperlink ref="F6" r:id="rId8"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1018,7 +1151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1098,18 +1231,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:E4">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
     <sortCondition ref="A2:A4"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1132,10 +1265,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>20</v>
@@ -1143,23 +1276,21 @@
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -1177,169 +1308,151 @@
       <c r="E3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>102</v>
-      </c>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>107</v>
-      </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>112</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="4" t="s">
         <v>117</v>
       </c>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1347,16 +1460,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1367,13 +1481,16 @@
       <c r="D1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1381,13 +1498,14 @@
       <c r="D2">
         <v>1970</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>1972</v>
@@ -1395,279 +1513,305 @@
       <c r="D3">
         <v>1973</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="D4">
         <v>1978</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>1969</v>
       </c>
       <c r="D5">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1970</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="D6">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1973</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>1970</v>
+        <v>1963</v>
       </c>
       <c r="D7">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1978</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D8">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1997</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9">
+        <v>1969</v>
+      </c>
+      <c r="D9">
         <v>1970</v>
       </c>
-      <c r="D9">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10">
+        <v>1970</v>
+      </c>
+      <c r="D10">
         <v>1971</v>
       </c>
-      <c r="D10">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D11">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1972</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12">
+        <v>1970</v>
+      </c>
+      <c r="D12">
         <v>1973</v>
       </c>
-      <c r="D12">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="D13">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1972</v>
+      </c>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="D14">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15">
-        <v>1979</v>
+        <v>1973</v>
       </c>
       <c r="D15">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16">
-        <v>1982</v>
+        <v>1973</v>
       </c>
       <c r="D16">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17">
-        <v>1982</v>
+        <v>1974</v>
       </c>
       <c r="D17">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1975</v>
+      </c>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D18">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19">
-        <v>1992</v>
+        <v>1982</v>
       </c>
       <c r="D19">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2007</v>
+      </c>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20">
-        <v>1992</v>
+        <v>1982</v>
       </c>
       <c r="D20">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1991</v>
+      </c>
+      <c r="E20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="D21">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1993</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="D22">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1993</v>
+      </c>
+      <c r="E22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23">
         <v>2002</v>
@@ -1675,106 +1819,453 @@
       <c r="D23">
         <v>2003</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24">
+        <v>2000</v>
+      </c>
+      <c r="D24">
         <v>2003</v>
       </c>
-      <c r="D24">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="D25">
         <v>2004</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D26">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2003</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27">
+        <v>2003</v>
+      </c>
+      <c r="D27">
         <v>2004</v>
       </c>
-      <c r="D27">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="D28">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2005</v>
+      </c>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="D29">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2005</v>
+      </c>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30">
         <v>2013</v>
       </c>
       <c r="D30">
+        <v>2013</v>
+      </c>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31">
+        <v>2013</v>
+      </c>
+      <c r="D31">
         <v>2017</v>
       </c>
+      <c r="E31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1968</v>
+      </c>
+      <c r="D2" s="9">
+        <v>1970</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1970</v>
+      </c>
+      <c r="D3" s="9">
+        <v>1978</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1978</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1987</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1987</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1990</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1990</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1993</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1993</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1996</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1996</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1999</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1999</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2002</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="9">
+        <v>2002</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2005</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2005</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2006</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2018</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2022</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2024</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2026</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="11">
+        <v>2026</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="4"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E15" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
 </file>
--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA9D0D2-C188-48FF-A065-F4F99C48089E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246DC85F-766E-462B-B73F-03F52A6A6D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="156">
   <si>
     <t>Name</t>
   </si>
@@ -178,9 +178,6 @@
     <t>To</t>
   </si>
   <si>
-    <t>Dr. Martin Ekse</t>
-  </si>
-  <si>
     <t>Dr. V.V. Silyanov MADI, Moscow, Russia</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
     <t>Dr. D.S.N.V. Amar Kumar</t>
   </si>
   <si>
-    <t>Dr. K.V.R. Ravi Shankar</t>
-  </si>
-  <si>
     <t>Prof. T.V. Ramanayya (Visiting Professor)</t>
   </si>
   <si>
@@ -469,19 +463,40 @@
     <t>Till Date</t>
   </si>
   <si>
+    <t>Dr. Martin Ekse, Washington University, USA</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/S.Raghava Chari.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/TS Reddy</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/B.P.Chandrashekhar</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/NV Rama Moorthy</t>
+  </si>
+  <si>
     <t>images/Previous Faculty/D.B. Srinivas.jpg</t>
   </si>
   <si>
     <t>images/Previous Faculty/V.R. Vinayaka Rao.jpg</t>
   </si>
   <si>
+    <t>images/Previous Faculty/N.Sadguna.jpg</t>
+  </si>
+  <si>
     <t>images/Previous Faculty/B.V. Kiran Kumar.jpg</t>
   </si>
   <si>
     <t>images/Previous Faculty/SSSV Gopal Raju.jpg</t>
   </si>
   <si>
-    <t>images/Previous Faculty/N. Sadguna.jpg</t>
+    <t>images/Previous Faculty/Amar Kumar.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/NV Rama Moorthy.jpg</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1025,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>29</v>
@@ -1047,7 +1062,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>8332969262</v>
@@ -1067,48 +1082,48 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>9849102935</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>89</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>8332969252</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>84</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1265,10 +1280,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>20</v>
@@ -1276,181 +1291,181 @@
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -1470,7 +1485,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1482,7 +1497,7 @@
         <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1490,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1505,7 +1520,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>1972</v>
@@ -1520,10 +1535,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="D4">
         <v>1978</v>
@@ -1535,28 +1550,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>1969</v>
       </c>
       <c r="D5">
-        <v>1970</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>1997</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="D6">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -1565,28 +1582,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>1963</v>
+        <v>1970</v>
       </c>
       <c r="D7">
-        <v>1978</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>1971</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D8">
-        <v>1997</v>
+        <v>1972</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -1595,13 +1614,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D9">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -1610,13 +1629,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D10">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -1625,13 +1644,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D11">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -1640,28 +1659,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D12">
-        <v>1973</v>
-      </c>
-      <c r="E12" s="4"/>
+        <v>2007</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="D13">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -1670,13 +1691,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="D14">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -1685,13 +1706,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="D15">
-        <v>2007</v>
+        <v>1981</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -1700,28 +1721,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="D16">
-        <v>1981</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>2007</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="D17">
-        <v>1975</v>
+        <v>1991</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -1730,13 +1753,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D18">
-        <v>1981</v>
+        <v>2000</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -1745,13 +1768,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="D19">
-        <v>2007</v>
+        <v>1993</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -1760,16 +1783,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="D20">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="E20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1777,16 +1800,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="D21">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1794,16 +1817,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="D22">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="E22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1811,7 +1834,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23">
         <v>2002</v>
@@ -1820,7 +1843,7 @@
         <v>2003</v>
       </c>
       <c r="E23" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1828,16 +1851,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D24">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1845,10 +1868,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D25">
         <v>2004</v>
@@ -1859,13 +1882,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D26">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="E26" s="4"/>
     </row>
@@ -1874,13 +1897,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D27">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="E27" s="4"/>
     </row>
@@ -1889,28 +1912,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="D28">
-        <v>2005</v>
-      </c>
-      <c r="E28" s="4"/>
+        <v>2013</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="D29">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="E29" s="4"/>
     </row>
@@ -1919,29 +1944,17 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30">
         <v>2013</v>
       </c>
       <c r="D30">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31">
-        <v>2013</v>
-      </c>
-      <c r="D31">
-        <v>2017</v>
-      </c>
       <c r="E31" s="4"/>
     </row>
   </sheetData>
@@ -1963,7 +1976,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -1983,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C2" s="9">
         <v>1968</v>
@@ -1998,7 +2011,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C3" s="9">
         <v>1970</v>
@@ -2013,7 +2026,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C4" s="9">
         <v>1978</v>
@@ -2021,14 +2034,16 @@
       <c r="D4" s="9">
         <v>1987</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C5" s="9">
         <v>1987</v>
@@ -2036,14 +2051,16 @@
       <c r="D5" s="9">
         <v>1990</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C6" s="9">
         <v>1990</v>
@@ -2051,14 +2068,16 @@
       <c r="D6" s="9">
         <v>1993</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C7" s="9">
         <v>1993</v>
@@ -2066,14 +2085,16 @@
       <c r="D7" s="9">
         <v>1996</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C8" s="9">
         <v>1996</v>
@@ -2081,14 +2102,16 @@
       <c r="D8" s="9">
         <v>1999</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" s="9">
         <v>1999</v>
@@ -2096,14 +2119,16 @@
       <c r="D9" s="9">
         <v>2002</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="9">
         <v>2002</v>
@@ -2111,7 +2136,7 @@
       <c r="D10" s="9">
         <v>2005</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2120,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C11" s="9">
         <v>2005</v>
@@ -2128,14 +2153,16 @@
       <c r="D11" s="9">
         <v>2006</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C12" s="9">
         <v>2006</v>
@@ -2152,7 +2179,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="9">
         <v>2018</v>
@@ -2161,7 +2188,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2169,7 +2196,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" s="9">
         <v>2022</v>
@@ -2186,7 +2213,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
@@ -2195,7 +2222,7 @@
         <v>2026</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2209,7 +2236,7 @@
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
@@ -2264,8 +2291,9 @@
   <hyperlinks>
     <hyperlink ref="E15" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="E10" r:id="rId3" xr:uid="{CF961E56-8C58-43C7-9E8E-C4C1CF4ECF88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246DC85F-766E-462B-B73F-03F52A6A6D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9328B2-0F97-4958-83F5-DCCFDDBA18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
   <si>
     <t>Name</t>
   </si>
@@ -469,24 +469,12 @@
     <t>images/Previous Faculty/S.Raghava Chari.jpg</t>
   </si>
   <si>
-    <t>images/Previous Faculty/TS Reddy</t>
-  </si>
-  <si>
-    <t>images/Previous Faculty/B.P.Chandrashekhar</t>
-  </si>
-  <si>
-    <t>images/Previous Faculty/NV Rama Moorthy</t>
-  </si>
-  <si>
     <t>images/Previous Faculty/D.B. Srinivas.jpg</t>
   </si>
   <si>
     <t>images/Previous Faculty/V.R. Vinayaka Rao.jpg</t>
   </si>
   <si>
-    <t>images/Previous Faculty/N.Sadguna.jpg</t>
-  </si>
-  <si>
     <t>images/Previous Faculty/B.V. Kiran Kumar.jpg</t>
   </si>
   <si>
@@ -497,6 +485,15 @@
   </si>
   <si>
     <t>images/Previous Faculty/NV Rama Moorthy.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/TS Reddy.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/B.P.Chandrashekhar.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/N. Sadguna.jpg</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1477,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.85546875" customWidth="1"/>
+    <col min="5" max="5" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1591,7 +1588,7 @@
         <v>1971</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1668,7 +1665,7 @@
         <v>2007</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1730,7 +1727,7 @@
         <v>2007</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1792,7 +1789,7 @@
         <v>1993</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1809,7 +1806,7 @@
         <v>2003</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1826,7 +1823,7 @@
         <v>2004</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1843,7 +1840,7 @@
         <v>2003</v>
       </c>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1860,7 +1857,7 @@
         <v>2004</v>
       </c>
       <c r="E24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1921,7 +1918,7 @@
         <v>2013</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2052,7 +2049,7 @@
         <v>1990</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2086,7 +2083,7 @@
         <v>1996</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2103,7 +2100,7 @@
         <v>1999</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2120,7 +2117,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2154,7 +2151,7 @@
         <v>2006</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9328B2-0F97-4958-83F5-DCCFDDBA18C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
   <si>
     <t>Name</t>
   </si>
@@ -494,12 +493,21 @@
   </si>
   <si>
     <t>images/Previous Faculty/N. Sadguna.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/K. Appala Raju.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/Dr. Francis Christopher.jpg</t>
+  </si>
+  <si>
+    <t>images/Previous Faculty/P. Sasanka Bhushan.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -949,7 +957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1144,18 +1152,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
+  <sortState ref="A2:G8">
     <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D4" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="F3" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D7" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in"/>
+    <hyperlink ref="F6" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1163,7 +1171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1243,18 +1251,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
+  <sortState ref="A2:E4">
     <sortCondition ref="A2:A4"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1472,7 +1480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1758,7 +1766,9 @@
       <c r="D18">
         <v>2000</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
@@ -1773,7 +1783,9 @@
       <c r="D19">
         <v>1993</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -1949,7 +1961,9 @@
       <c r="D30">
         <v>2017</v>
       </c>
-      <c r="E30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E31" s="4"/>
@@ -1960,7 +1974,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2286,9 +2300,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="E13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="E10" r:id="rId3" xr:uid="{CF961E56-8C58-43C7-9E8E-C4C1CF4ECF88}"/>
+    <hyperlink ref="E15" r:id="rId1"/>
+    <hyperlink ref="E13" r:id="rId2"/>
+    <hyperlink ref="E10" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\mainnn\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1586BB-83AC-43AF-A2D9-B22E9CE76B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -502,12 +503,30 @@
   </si>
   <si>
     <t>images/Previous Faculty/P. Sasanka Bhushan.jpg</t>
+  </si>
+  <si>
+    <t>bio sketch</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Publications</t>
+  </si>
+  <si>
+    <t>Doctoral Students</t>
+  </si>
+  <si>
+    <t>PROJECTS</t>
+  </si>
+  <si>
+    <t>PATENTS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -957,213 +976,304 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="102.7109375" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="1" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.42578125" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
+    <col min="14" max="15" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="C2">
+      <c r="I2">
         <v>8332969421</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3">
+        <v>62</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>31</v>
       </c>
-      <c r="C3">
+      <c r="I3">
         <v>8879425755</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="K3" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="M3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="L4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="M4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>72</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
         <v>80</v>
       </c>
-      <c r="C5">
+      <c r="I5">
         <v>8332969262</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" t="s">
+      <c r="K5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s">
+      <c r="L5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>85</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>106</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
         <v>80</v>
       </c>
-      <c r="C6">
+      <c r="I6">
         <v>9849102935</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E6" t="s">
+      <c r="K6" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G6" t="s">
+      <c r="M6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>79</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
         <v>80</v>
       </c>
-      <c r="C7">
+      <c r="I7">
         <v>8332969252</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E7" t="s">
+      <c r="K7" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G7" t="s">
+      <c r="M7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="J8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+      <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="F8" t="s">
+      <c r="L8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
+      <c r="M8" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
     <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="F3" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D7" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="D6" r:id="rId7" display="mailto:ss@nitw.ac.in"/>
-    <hyperlink ref="F6" r:id="rId8"/>
+    <hyperlink ref="J4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="J7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="L7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="L6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1171,7 +1281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1251,18 +1361,18 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:E4">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E4">
     <sortCondition ref="A2:A4"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1480,7 +1590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1974,7 +2084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2300,9 +2410,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1"/>
-    <hyperlink ref="E13" r:id="rId2"/>
-    <hyperlink ref="E10" r:id="rId3"/>
+    <hyperlink ref="E15" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="E10" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1586BB-83AC-43AF-A2D9-B22E9CE76B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD31B2D8-A205-41C2-B8F9-1F9CB3A2C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="183">
   <si>
     <t>Name</t>
   </si>
@@ -521,13 +521,70 @@
   </si>
   <si>
     <t>PATENTS</t>
+  </si>
+  <si>
+    <t>PhD Institute</t>
+  </si>
+  <si>
+    <t>Masters Institute</t>
+  </si>
+  <si>
+    <t>Indian Institute of Technology Roorkee</t>
+  </si>
+  <si>
+    <t>Indian Institute of Technology Guwahati</t>
+  </si>
+  <si>
+    <t>IIT Bombay</t>
+  </si>
+  <si>
+    <t>NIT Warangal</t>
+  </si>
+  <si>
+    <t>JNTU Hyderabad</t>
+  </si>
+  <si>
+    <t>National Institute of Technology Warangal</t>
+  </si>
+  <si>
+    <t>Indian Institute of Technology Madras</t>
+  </si>
+  <si>
+    <t>IIT Kharagpur</t>
+  </si>
+  <si>
+    <t>ORCID</t>
+  </si>
+  <si>
+    <t>Scopus</t>
+  </si>
+  <si>
+    <t>GoogleScholar</t>
+  </si>
+  <si>
+    <t>0000-0002-1680-2089</t>
+  </si>
+  <si>
+    <t>0000-0002-0636-1355</t>
+  </si>
+  <si>
+    <t>0000-0001-6648-2493</t>
+  </si>
+  <si>
+    <t>0000-0002-5458-3972</t>
+  </si>
+  <si>
+    <t>0000-0001-6156-4625</t>
+  </si>
+  <si>
+    <t>0000-0001-9721-1557</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,16 +627,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -659,12 +728,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -696,6 +780,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -977,23 +1068,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="80.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38.42578125" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" customWidth="1"/>
-    <col min="14" max="15" width="9" customWidth="1"/>
+    <col min="7" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="21.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38.42578125" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" customWidth="1"/>
+    <col min="19" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1016,25 +1110,40 @@
         <v>159</v>
       </c>
       <c r="H1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" t="s">
+        <v>176</v>
+      </c>
+      <c r="M1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1044,26 +1153,38 @@
       <c r="D2">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2">
+        <v>55978788300</v>
+      </c>
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="I2">
+      <c r="N2">
         <v>8332969421</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" t="s">
+      <c r="Q2" t="s">
         <v>34</v>
       </c>
-      <c r="M2" t="s">
+      <c r="R2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1079,26 +1200,38 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K3">
+        <v>56237024300</v>
+      </c>
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="I3">
+      <c r="N3">
         <v>8879425755</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>78</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="R3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1111,26 +1244,38 @@
       <c r="E4">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K4">
+        <v>55024478300</v>
+      </c>
+      <c r="M4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L4" t="s">
+      <c r="Q4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" t="s">
+      <c r="R4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1146,26 +1291,38 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5">
+        <v>57193253075</v>
+      </c>
+      <c r="M5" t="s">
         <v>80</v>
       </c>
-      <c r="I5">
+      <c r="N5">
         <v>8332969262</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
         <v>38</v>
       </c>
-      <c r="L5" t="s">
+      <c r="Q5" t="s">
         <v>39</v>
       </c>
-      <c r="M5" t="s">
+      <c r="R5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -1181,26 +1338,38 @@
       <c r="F6">
         <v>3</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="J6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K6">
+        <v>57211683260</v>
+      </c>
+      <c r="M6" t="s">
         <v>80</v>
       </c>
-      <c r="I6">
+      <c r="N6">
         <v>9849102935</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K6" t="s">
+      <c r="P6" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M6" t="s">
+      <c r="R6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1213,26 +1382,32 @@
       <c r="E7">
         <v>7</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="M7" t="s">
         <v>80</v>
       </c>
-      <c r="I7">
+      <c r="N7">
         <v>8332969252</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
         <v>82</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M7" t="s">
+      <c r="R7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1245,35 +1420,47 @@
       <c r="E8">
         <v>9</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8">
+        <v>57192237169</v>
+      </c>
+      <c r="M8" t="s">
         <v>12</v>
       </c>
-      <c r="J8" t="s">
+      <c r="O8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
         <v>26</v>
       </c>
-      <c r="L8" t="s">
+      <c r="Q8" t="s">
         <v>28</v>
       </c>
-      <c r="M8" t="s">
+      <c r="R8" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R8">
     <sortCondition ref="A5:A8"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="L3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="L7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="L6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="Q3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="Q7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="Q6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD31B2D8-A205-41C2-B8F9-1F9CB3A2C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B692D-A98A-40E4-8024-09FAFF2F07C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -784,7 +784,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1236,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="D4">
         <v>13</v>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B692D-A98A-40E4-8024-09FAFF2F07C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3E2C8E-3252-4B3E-8233-E3699052CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="144">
   <si>
     <t>Name</t>
   </si>
@@ -307,126 +307,6 @@
     <t>Research Areas</t>
   </si>
   <si>
-    <t>Dr. Ananya Sharma</t>
-  </si>
-  <si>
-    <t>+91 98765 43210</t>
-  </si>
-  <si>
-    <t>ananya.sharma@university.edu</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Machine Learning, Data Analytics</t>
-  </si>
-  <si>
-    <t>Dr. Rahul Verma</t>
-  </si>
-  <si>
-    <t>+91 98765 43211</t>
-  </si>
-  <si>
-    <t>rahul.verma@university.edu</t>
-  </si>
-  <si>
-    <t>Computer Vision, Image Processing, Deep Learning</t>
-  </si>
-  <si>
-    <t>Dr. Priya Nair</t>
-  </si>
-  <si>
-    <t>+91 98765 43212</t>
-  </si>
-  <si>
-    <t>priya.nair@university.edu</t>
-  </si>
-  <si>
-    <t>Cyber Security, Network Security, Cryptography</t>
-  </si>
-  <si>
-    <t>Dr. Karthik Reddy</t>
-  </si>
-  <si>
-    <t>+91 98765 43213</t>
-  </si>
-  <si>
-    <t>karthik.reddy@university.edu</t>
-  </si>
-  <si>
-    <t>Internet of Things (IoT), Embedded Systems</t>
-  </si>
-  <si>
-    <t>Dr. Sneha Gupta</t>
-  </si>
-  <si>
-    <t>+91 98765 43214</t>
-  </si>
-  <si>
-    <t>sneha.gupta@university.edu</t>
-  </si>
-  <si>
-    <t>Natural Language Processing, Generative AI</t>
-  </si>
-  <si>
-    <t>Dr. Arjun Mehta</t>
-  </si>
-  <si>
-    <t>+91 98765 43215</t>
-  </si>
-  <si>
-    <t>arjun.mehta@university.edu</t>
-  </si>
-  <si>
-    <t>Big Data Analytics, Cloud Computing</t>
-  </si>
-  <si>
-    <t>Dr. Neha Kapoor</t>
-  </si>
-  <si>
-    <t>+91 98765 43216</t>
-  </si>
-  <si>
-    <t>neha.kapoor@university.edu</t>
-  </si>
-  <si>
-    <t>Human-Computer Interaction, UX Design</t>
-  </si>
-  <si>
-    <t>Dr. Vikram Singh</t>
-  </si>
-  <si>
-    <t>+91 98765 43217</t>
-  </si>
-  <si>
-    <t>vikram.singh@university.edu</t>
-  </si>
-  <si>
-    <t>Robotics, Autonomous Systems</t>
-  </si>
-  <si>
-    <t>Dr. Pooja Menon</t>
-  </si>
-  <si>
-    <t>+91 98765 43218</t>
-  </si>
-  <si>
-    <t>pooja.menon@university.edu</t>
-  </si>
-  <si>
-    <t>Data Science, Business Intelligence</t>
-  </si>
-  <si>
-    <t>Dr. Rohan Das</t>
-  </si>
-  <si>
-    <t>+91 98765 43219</t>
-  </si>
-  <si>
-    <t>rohan.das@university.edu</t>
-  </si>
-  <si>
-    <t>Software Engineering, Distributed Systems</t>
-  </si>
-  <si>
     <t>S. No.</t>
   </si>
   <si>
@@ -578,6 +458,9 @@
   </si>
   <si>
     <t>0000-0001-9721-1557</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -1092,37 +975,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="I1" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="J1" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="K1" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L1" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="M1" t="s">
         <v>1</v>
@@ -1154,13 +1037,13 @@
         <v>8</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="K2">
         <v>55978788300</v>
@@ -1201,13 +1084,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="J3" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="K3">
         <v>56237024300</v>
@@ -1245,13 +1128,13 @@
         <v>8</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="J4" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="K4">
         <v>55024478300</v>
@@ -1292,13 +1175,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="J5" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="K5">
         <v>57193253075</v>
@@ -1339,13 +1222,13 @@
         <v>3</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="J6" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="K6">
         <v>57211683260</v>
@@ -1383,10 +1266,10 @@
         <v>7</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="M7" t="s">
         <v>80</v>
@@ -1421,13 +1304,13 @@
         <v>9</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="J8" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="K8">
         <v>57192237169</v>
@@ -1591,184 +1474,100 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>95</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>103</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>111</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>115</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>127</v>
-      </c>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>131</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
   </sheetData>
@@ -1799,7 +1598,7 @@
         <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1807,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1861,7 +1660,7 @@
         <v>1997</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1893,7 +1692,7 @@
         <v>1971</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1970,7 +1769,7 @@
         <v>2007</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2032,7 +1831,7 @@
         <v>2007</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2064,7 +1863,7 @@
         <v>2000</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2081,7 +1880,7 @@
         <v>1993</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2098,7 +1897,7 @@
         <v>1993</v>
       </c>
       <c r="E20" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2115,7 +1914,7 @@
         <v>2003</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2132,7 +1931,7 @@
         <v>2004</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2149,7 +1948,7 @@
         <v>2003</v>
       </c>
       <c r="E23" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2166,7 +1965,7 @@
         <v>2004</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2227,7 +2026,7 @@
         <v>2013</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2259,7 +2058,7 @@
         <v>2017</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2284,7 +2083,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2304,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="C2" s="9">
         <v>1968</v>
@@ -2319,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C3" s="9">
         <v>1970</v>
@@ -2334,7 +2133,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="C4" s="9">
         <v>1978</v>
@@ -2343,7 +2142,7 @@
         <v>1987</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2351,7 +2150,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C5" s="9">
         <v>1987</v>
@@ -2360,7 +2159,7 @@
         <v>1990</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2368,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="C6" s="9">
         <v>1990</v>
@@ -2377,7 +2176,7 @@
         <v>1993</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2385,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C7" s="9">
         <v>1993</v>
@@ -2394,7 +2193,7 @@
         <v>1996</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2402,7 +2201,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9">
         <v>1996</v>
@@ -2411,7 +2210,7 @@
         <v>1999</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2419,7 +2218,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9">
         <v>1999</v>
@@ -2428,7 +2227,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2436,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="C10" s="9">
         <v>2002</v>
@@ -2453,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C11" s="9">
         <v>2005</v>
@@ -2462,7 +2261,7 @@
         <v>2006</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2470,7 +2269,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="C12" s="9">
         <v>2006</v>
@@ -2487,7 +2286,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C13" s="9">
         <v>2018</v>
@@ -2504,7 +2303,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="C14" s="9">
         <v>2022</v>
@@ -2521,7 +2320,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
@@ -2544,7 +2343,7 @@
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3E2C8E-3252-4B3E-8233-E3699052CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFAB7D5-68BF-464F-9842-CCDA56C08B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -1036,6 +1036,9 @@
       <c r="D2">
         <v>8</v>
       </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="H2" s="13" t="s">
         <v>126</v>
       </c>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFAB7D5-68BF-464F-9842-CCDA56C08B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CF74B5-A67D-455B-B7E8-6F22FDFA9619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
   <si>
     <t>Name</t>
   </si>
@@ -277,9 +277,6 @@
     <t>vc@nitw.ac.in</t>
   </si>
   <si>
-    <t>Characterization for asphalt binders and mixtures; asphalt pavement analysis, design and evaluation; quantification of roadway and railway traffic noise.</t>
-  </si>
-  <si>
     <t>https://erp.nitw.ac.in/ext/profile/getUserImage/ce-vc</t>
   </si>
   <si>
@@ -442,25 +439,73 @@
     <t>GoogleScholar</t>
   </si>
   <si>
-    <t>0000-0002-1680-2089</t>
-  </si>
-  <si>
-    <t>0000-0002-0636-1355</t>
-  </si>
-  <si>
-    <t>0000-0001-6648-2493</t>
-  </si>
-  <si>
-    <t>0000-0002-5458-3972</t>
-  </si>
-  <si>
-    <t>0000-0001-6156-4625</t>
-  </si>
-  <si>
-    <t>0000-0001-9721-1557</t>
-  </si>
-  <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1680-2089</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=55978788300</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=xTk4D4MAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-0636-1355</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=56237024300</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=53QkKr0AAAAJ&amp;hl=en&amp;hl=en&amp;oi=ao</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-6648-2493</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=55024478300</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=vQY32bgAAAAJ&amp;hl=en&amp;oi=ao</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-5458-3972</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=57193253075</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=iF0VKOkAAAAJ&amp;hl=en&amp;oi=ao</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-6156-4625</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=57211683260</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=AjQSr0gAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://orcid.org/https://orcid.org/0000-0003-4929-7055</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-9721-1557</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=57192237169</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=xtd6bvAAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?view_op=new_profile&amp;hl=en</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=57193680699</t>
+  </si>
+  <si>
+    <t>Characterization for asphalt binders and mixtures; asphalt pavement analysis, design and evaluation; quantification of roadway and railway traffic noise</t>
   </si>
 </sst>
 </file>
@@ -667,7 +712,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -975,37 +1020,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
         <v>118</v>
       </c>
-      <c r="C1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>124</v>
       </c>
-      <c r="I1" t="s">
-        <v>125</v>
-      </c>
       <c r="J1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
         <v>134</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>135</v>
-      </c>
-      <c r="L1" t="s">
-        <v>136</v>
       </c>
       <c r="M1" t="s">
         <v>1</v>
@@ -1040,16 +1085,19 @@
         <v>2</v>
       </c>
       <c r="H2" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>127</v>
       </c>
       <c r="J2" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="K2">
-        <v>55978788300</v>
+      <c r="K2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="M2" t="s">
         <v>31</v>
@@ -1087,16 +1135,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K3">
-        <v>56237024300</v>
+      <c r="J3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="M3" t="s">
         <v>31</v>
@@ -1131,16 +1182,19 @@
         <v>8</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K4">
-        <v>55024478300</v>
+        <v>128</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L4" t="s">
+        <v>145</v>
       </c>
       <c r="M4" t="s">
         <v>6</v>
@@ -1178,16 +1232,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K5">
-        <v>57193253075</v>
+        <v>146</v>
+      </c>
+      <c r="K5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L5" t="s">
+        <v>148</v>
       </c>
       <c r="M5" t="s">
         <v>80</v>
@@ -1210,7 +1267,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>106</v>
@@ -1225,16 +1282,19 @@
         <v>3</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K6">
-        <v>57211683260</v>
+        <v>149</v>
+      </c>
+      <c r="K6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L6" t="s">
+        <v>151</v>
       </c>
       <c r="M6" t="s">
         <v>80</v>
@@ -1243,16 +1303,16 @@
         <v>9849102935</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P6" t="s">
         <v>86</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" t="s">
         <v>88</v>
-      </c>
-      <c r="R6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1269,10 +1329,19 @@
         <v>7</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="J7" t="s">
+        <v>152</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" t="s">
+        <v>156</v>
       </c>
       <c r="M7" t="s">
         <v>80</v>
@@ -1284,13 +1353,13 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" t="s">
         <v>83</v>
-      </c>
-      <c r="R7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1307,16 +1376,19 @@
         <v>9</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J8" t="s">
-        <v>142</v>
-      </c>
-      <c r="K8">
-        <v>57192237169</v>
+        <v>153</v>
+      </c>
+      <c r="K8" t="s">
+        <v>154</v>
+      </c>
+      <c r="L8" t="s">
+        <v>155</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -1347,9 +1419,18 @@
     <hyperlink ref="Q7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="O6" r:id="rId7" display="mailto:ss@nitw.ac.in" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="Q6" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J2" r:id="rId9" xr:uid="{DC9A0E4E-B807-4235-9E06-3DA494530748}"/>
+    <hyperlink ref="K2" r:id="rId10" xr:uid="{D4AA87D4-EE9D-418E-AAD9-37076F1469C3}"/>
+    <hyperlink ref="L2" r:id="rId11" xr:uid="{4844F781-5DCE-4882-AE98-E6E9FC30794E}"/>
+    <hyperlink ref="J3" r:id="rId12" xr:uid="{DD6C7318-5A81-4641-A7DB-2A89307ED38E}"/>
+    <hyperlink ref="K3" r:id="rId13" xr:uid="{D9DC149D-358B-4854-8D27-DA6278000CE2}"/>
+    <hyperlink ref="L3" r:id="rId14" xr:uid="{8D08A87C-3DA1-4452-A5D0-9ED0278D7DC9}"/>
+    <hyperlink ref="J4" r:id="rId15" xr:uid="{9016028E-4940-4B37-8F76-7CE23FF15518}"/>
+    <hyperlink ref="K4" r:id="rId16" xr:uid="{BB57349D-FB9C-42D2-88DB-7A03D3434110}"/>
+    <hyperlink ref="K7" r:id="rId17" xr:uid="{BD3F1E5C-F3B3-46C3-A61C-1A5F6DDAC098}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -1468,10 +1549,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>20</v>
@@ -1479,7 +1560,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1489,7 +1570,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1499,7 +1580,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1509,7 +1590,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1519,7 +1600,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1529,7 +1610,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1539,7 +1620,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1549,7 +1630,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1601,7 +1682,7 @@
         <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1609,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1663,7 +1744,7 @@
         <v>1997</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1695,7 +1776,7 @@
         <v>1971</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1772,7 +1853,7 @@
         <v>2007</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1834,7 +1915,7 @@
         <v>2007</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1866,7 +1947,7 @@
         <v>2000</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1883,7 +1964,7 @@
         <v>1993</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,7 +1981,7 @@
         <v>1993</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1917,7 +1998,7 @@
         <v>2003</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1934,7 +2015,7 @@
         <v>2004</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1951,7 +2032,7 @@
         <v>2003</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1968,7 +2049,7 @@
         <v>2004</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,7 +2110,7 @@
         <v>2013</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2061,7 +2142,7 @@
         <v>2017</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2086,7 +2167,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2106,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="9">
         <v>1968</v>
@@ -2121,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="9">
         <v>1970</v>
@@ -2136,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="9">
         <v>1978</v>
@@ -2145,7 +2226,7 @@
         <v>1987</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2153,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="9">
         <v>1987</v>
@@ -2162,7 +2243,7 @@
         <v>1990</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2170,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="9">
         <v>1990</v>
@@ -2179,7 +2260,7 @@
         <v>1993</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2187,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="9">
         <v>1993</v>
@@ -2196,7 +2277,7 @@
         <v>1996</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2204,7 +2285,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="9">
         <v>1996</v>
@@ -2213,7 +2294,7 @@
         <v>1999</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2221,7 +2302,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="9">
         <v>1999</v>
@@ -2230,7 +2311,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2238,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="9">
         <v>2002</v>
@@ -2255,7 +2336,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="9">
         <v>2005</v>
@@ -2264,7 +2345,7 @@
         <v>2006</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2272,7 +2353,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="9">
         <v>2006</v>
@@ -2289,7 +2370,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" s="9">
         <v>2018</v>
@@ -2298,7 +2379,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2306,7 +2387,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9">
         <v>2022</v>
@@ -2323,7 +2404,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
@@ -2332,7 +2413,7 @@
         <v>2026</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2346,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
